--- a/data/trans_orig/P1805_2016_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1805_2016_2023-Provincia-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5324</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20260</t>
+          <t>19454</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12654</t>
+          <t>13557</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31653</t>
+          <t>32483</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21731</t>
+          <t>21925</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44931</t>
+          <t>46095</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>273501</t>
+          <t>274307</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>288437</t>
+          <t>288444</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>257050</t>
+          <t>256220</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>276049</t>
+          <t>275146</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>537533</t>
+          <t>536369</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>560733</t>
+          <t>560539</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,24%</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7157</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11871</t>
+          <t>12245</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3964</t>
+          <t>3913</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15556</t>
+          <t>15094</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>495418</t>
+          <t>495970</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>511213</t>
+          <t>510839</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>521032</t>
+          <t>521102</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1010103</t>
+          <t>1010565</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1021695</t>
+          <t>1021746</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12593</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8505</t>
+          <t>8219</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25129</t>
+          <t>24924</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11885</t>
+          <t>12069</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31187</t>
+          <t>31668</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>305972</t>
+          <t>307234</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316359</t>
+          <t>316642</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>311180</t>
+          <t>311385</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>327804</t>
+          <t>328090</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>623687</t>
+          <t>623206</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>642989</t>
+          <t>642805</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16911</t>
+          <t>17233</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6347</t>
+          <t>6936</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20675</t>
+          <t>21864</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13898</t>
+          <t>13729</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32292</t>
+          <t>32694</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>353053</t>
+          <t>352731</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>366608</t>
+          <t>365419</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>380936</t>
+          <t>380347</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>724955</t>
+          <t>724553</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>743349</t>
+          <t>743518</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2814</t>
+          <t>2537</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13903</t>
+          <t>13387</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>957</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9293</t>
+          <t>8683</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17579</t>
+          <t>18057</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>197318</t>
+          <t>197834</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>208407</t>
+          <t>208684</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>209294</t>
+          <t>209904</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>217628</t>
+          <t>217630</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>412229</t>
+          <t>411751</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>424385</t>
+          <t>424979</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7868</t>
+          <t>7518</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18137</t>
+          <t>18148</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7321</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23299</t>
+          <t>22426</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>255255</t>
+          <t>255605</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262146</t>
+          <t>263123</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>254978</t>
+          <t>254967</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>267770</t>
+          <t>267885</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>512939</t>
+          <t>513812</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>528917</t>
+          <t>528933</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,64%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13084</t>
+          <t>13901</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14572</t>
+          <t>14290</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35532</t>
+          <t>36785</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19779</t>
+          <t>19866</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43511</t>
+          <t>42458</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>643474</t>
+          <t>642657</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>654267</t>
+          <t>654181</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>655762</t>
+          <t>654509</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>676722</t>
+          <t>677004</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1304341</t>
+          <t>1305394</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1328073</t>
+          <t>1327986</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10826</t>
+          <t>11427</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>28061</t>
+          <t>27634</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>26637</t>
+          <t>26749</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>53662</t>
+          <t>53404</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>42175</t>
+          <t>42722</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>73425</t>
+          <t>73133</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>750522</t>
+          <t>750949</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>767757</t>
+          <t>767156</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>772505</t>
+          <t>772763</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>799530</t>
+          <t>799418</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1531325</t>
+          <t>1531617</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1562575</t>
+          <t>1562028</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -3475,12 +3475,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>47645</t>
+          <t>47184</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>77454</t>
+          <t>78455</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>110010</t>
+          <t>108863</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>160910</t>
+          <t>155830</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>167506</t>
+          <t>164728</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>223618</t>
+          <t>223541</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3316896</t>
+          <t>3315895</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3346705</t>
+          <t>3347166</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3383632</t>
+          <t>3388712</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3434532</t>
+          <t>3435679</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6715274</t>
+          <t>6715351</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6771386</t>
+          <t>6774164</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -4049,32 +4049,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11774</t>
+          <t>7960</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4084,32 +4084,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7734</t>
+          <t>8212</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4550</t>
+          <t>4820</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13420</t>
+          <t>13097</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4119,32 +4119,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>11357</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6738</t>
+          <t>6714</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18280</t>
+          <t>18861</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -4162,32 +4162,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>307752</t>
+          <t>315700</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>299669</t>
+          <t>310885</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>310440</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4197,32 +4197,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>281901</t>
+          <t>307849</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>276215</t>
+          <t>302964</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285085</t>
+          <t>311241</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4232,32 +4232,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>589652</t>
+          <t>623549</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>582797</t>
+          <t>616045</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>594339</t>
+          <t>628192</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -4275,17 +4275,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4310,17 +4310,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4345,17 +4345,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20484</t>
+          <t>19860</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11586</t>
+          <t>12100</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38029</t>
+          <t>35817</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20973</t>
+          <t>21269</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12926</t>
+          <t>14553</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31712</t>
+          <t>34434</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4462,32 +4462,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>41457</t>
+          <t>41129</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29215</t>
+          <t>29078</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58830</t>
+          <t>57887</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -4505,32 +4505,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>497906</t>
+          <t>510787</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>480361</t>
+          <t>494830</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>506804</t>
+          <t>518547</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>492752</t>
+          <t>523944</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>482013</t>
+          <t>510779</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>500799</t>
+          <t>530660</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4575,32 +4575,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>990658</t>
+          <t>1034731</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>973285</t>
+          <t>1017973</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1002900</t>
+          <t>1046782</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -4618,17 +4618,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4688,17 +4688,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1032115</t>
+          <t>1075860</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1032115</t>
+          <t>1075860</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1032115</t>
+          <t>1075860</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4735,32 +4735,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>9380</t>
+          <t>10526</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4817</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17662</t>
+          <t>19826</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>18993</t>
+          <t>19177</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>13576</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27227</t>
+          <t>28017</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4805,32 +4805,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>28373</t>
+          <t>29703</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20297</t>
+          <t>21015</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40381</t>
+          <t>40519</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -4848,32 +4848,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>306670</t>
+          <t>305467</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>298388</t>
+          <t>296167</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>311233</t>
+          <t>310832</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>330135</t>
+          <t>337204</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>321901</t>
+          <t>328364</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>335786</t>
+          <t>342805</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4918,32 +4918,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>636805</t>
+          <t>642672</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>624797</t>
+          <t>631856</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>644881</t>
+          <t>651360</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,87%</t>
         </is>
       </c>
     </row>
@@ -4961,17 +4961,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4996,17 +4996,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5031,17 +5031,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5078,67 +5078,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20469</t>
+          <t>21524</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11991</t>
+          <t>12278</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33477</t>
+          <t>34296</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,19%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>24601</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>16188</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>35548</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>5,83%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
           <t>3,84%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,71%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>21690</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>11823</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>32920</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,56%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5148,32 +5148,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>42159</t>
+          <t>46125</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27774</t>
+          <t>33675</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59064</t>
+          <t>63051</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -5191,69 +5191,69 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>292088</t>
+          <t>351621</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>279080</t>
+          <t>338849</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>300566</t>
+          <t>360867</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>96,71%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>569</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>397360</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>386413</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>405773</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>94,17%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>91,58%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>96,16%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>569</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>454028</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>442798</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>463895</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,44%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>93,08%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>97,51%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>844</t>
@@ -5261,32 +5261,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>746115</t>
+          <t>748982</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>729210</t>
+          <t>732056</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>760500</t>
+          <t>761432</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>95,76%</t>
         </is>
       </c>
     </row>
@@ -5304,17 +5304,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5339,17 +5339,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5374,17 +5374,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>1486</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4290</t>
+          <t>5057</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5456,32 +5456,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1577</t>
+          <t>1487</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6485</t>
+          <t>6692</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5491,32 +5491,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>4854</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2390</t>
+          <t>2490</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8797</t>
+          <t>9020</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -5534,27 +5534,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>177376</t>
+          <t>204179</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>174452</t>
+          <t>200608</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>205418</t>
+          <t>223847</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>202171</t>
+          <t>220523</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>207079</t>
+          <t>225728</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5604,32 +5604,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>382794</t>
+          <t>428025</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>378601</t>
+          <t>423859</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>385008</t>
+          <t>430389</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -5647,17 +5647,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5682,17 +5682,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5717,17 +5717,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5764,32 +5764,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12203</t>
+          <t>12741</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5799,32 +5799,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8630</t>
+          <t>9241</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>5358</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13610</t>
+          <t>14638</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5834,32 +5834,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>15682</t>
+          <t>15995</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10270</t>
+          <t>11081</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21911</t>
+          <t>22939</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -5877,32 +5877,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>262584</t>
+          <t>263953</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>257433</t>
+          <t>257966</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266211</t>
+          <t>267223</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5912,32 +5912,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>248426</t>
+          <t>254509</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>243446</t>
+          <t>249112</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>251810</t>
+          <t>258392</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5947,32 +5947,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>511010</t>
+          <t>518462</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>504781</t>
+          <t>511518</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>516422</t>
+          <t>523376</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -5990,17 +5990,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6025,17 +6025,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6060,17 +6060,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6107,32 +6107,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>31240</t>
+          <t>34213</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19288</t>
+          <t>21824</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48038</t>
+          <t>54125</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6142,32 +6142,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>45028</t>
+          <t>49891</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18706</t>
+          <t>37228</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64977</t>
+          <t>67053</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6177,32 +6177,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>76268</t>
+          <t>84104</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>49400</t>
+          <t>66111</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>102823</t>
+          <t>107360</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -6220,32 +6220,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>593039</t>
+          <t>685474</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>576241</t>
+          <t>665562</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>604991</t>
+          <t>697863</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6255,32 +6255,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>804237</t>
+          <t>722166</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>784288</t>
+          <t>705004</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>830559</t>
+          <t>734829</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6290,32 +6290,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1397276</t>
+          <t>1407640</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1370721</t>
+          <t>1384384</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1424144</t>
+          <t>1425633</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>
@@ -6333,17 +6333,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6368,17 +6368,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6403,17 +6403,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6450,32 +6450,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>17243</t>
+          <t>19656</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6680</t>
+          <t>11825</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29636</t>
+          <t>29853</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6485,17 +6485,17 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>18524</t>
+          <t>21434</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12800</t>
+          <t>14583</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26839</t>
+          <t>31106</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -6520,32 +6520,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>35766</t>
+          <t>41091</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21468</t>
+          <t>30965</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>49114</t>
+          <t>54412</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -6563,32 +6563,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>911477</t>
+          <t>778416</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>899084</t>
+          <t>768219</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>922040</t>
+          <t>786247</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6598,17 +6598,17 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>699207</t>
+          <t>809897</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>690892</t>
+          <t>800225</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>704931</t>
+          <t>816748</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6633,32 +6633,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1610686</t>
+          <t>1588312</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1597338</t>
+          <t>1574991</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1624984</t>
+          <t>1598438</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -6676,17 +6676,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6711,17 +6711,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6746,17 +6746,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6793,32 +6793,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>110924</t>
+          <t>117165</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>83475</t>
+          <t>92163</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>141676</t>
+          <t>144233</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6828,32 +6828,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>144810</t>
+          <t>157192</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>114398</t>
+          <t>135152</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>170710</t>
+          <t>181297</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6863,32 +6863,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>255734</t>
+          <t>274357</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>220482</t>
+          <t>240328</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>297091</t>
+          <t>309782</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -6906,32 +6906,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3348893</t>
+          <t>3415597</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3318141</t>
+          <t>3388529</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3376342</t>
+          <t>3440599</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6941,32 +6941,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3516103</t>
+          <t>3576778</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3490203</t>
+          <t>3552673</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3546515</t>
+          <t>3598818</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6976,32 +6976,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6864996</t>
+          <t>6992375</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6823639</t>
+          <t>6956950</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6900248</t>
+          <t>7026404</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,69%</t>
         </is>
       </c>
     </row>
@@ -7019,17 +7019,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7054,17 +7054,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3660913</t>
+          <t>3733970</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3660913</t>
+          <t>3733970</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3660913</t>
+          <t>3733970</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7089,17 +7089,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7120730</t>
+          <t>7266732</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7120730</t>
+          <t>7266732</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7120730</t>
+          <t>7266732</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
